--- a/templates/CAPITANIA CW1 - template.xlsx
+++ b/templates/CAPITANIA CW1 - template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$44</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -803,12 +803,12 @@
     <xf numFmtId="0" fontId="36" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1261,7 +1261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="14.7109375" bestFit="1" customWidth="1" style="58" min="1" max="1"/>
@@ -1269,8 +1269,8 @@
     <col width="5.42578125" customWidth="1" style="58" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="58" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="58" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="58" min="10" max="19"/>
-    <col width="9.140625" customWidth="1" style="58" min="20" max="16384"/>
+    <col width="9.140625" customWidth="1" style="58" min="10" max="20"/>
+    <col width="9.140625" customWidth="1" style="58" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1422,96 +1422,96 @@
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B18" s="36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C18" s="37" t="n">
-        <v>3.47846889</v>
+        <v>3.49172269</v>
       </c>
       <c r="D18" s="38" t="n">
-        <v>0.0001931021098147134</v>
+        <v>0.0007609081076533908</v>
       </c>
       <c r="E18" s="38" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="39" t="n">
-        <v>0.3558420927968747</v>
+        <v>1.402175945738224</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C19" s="41" t="n">
-        <v>3.47779732</v>
+        <v>3.48906783</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>-0.006796305237141809</v>
+        <v>-0.0006171734937135964</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="43" t="n">
-        <v>-12.52400339484344</v>
+        <v>-1.137306618930951</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C20" s="41" t="n">
-        <v>3.50159523</v>
+        <v>3.49122252</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>-0.0004010562226272052</v>
+        <v>0.001646621024502082</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="43" t="n">
-        <v>-0.7390529586953275</v>
+        <v>3.034338008861616</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B21" s="40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C21" s="41" t="n">
-        <v>3.50300013</v>
+        <v>3.48548325</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>-2.583433018399361e-05</v>
+        <v>-0.002020540883873045</v>
       </c>
       <c r="E21" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="43" t="n">
-        <v>-0.04760663737697443</v>
+        <v>-3.723384987294674</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B22" s="40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C22" s="41" t="n">
-        <v>3.50309063</v>
+        <v>3.49254007</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>0.001404013289039385</v>
+        <v>0.0005434700697164452</v>
       </c>
       <c r="E22" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="43" t="n">
-        <v>2.587268609161155</v>
+        <v>1.00148842063883</v>
       </c>
     </row>
     <row r="23" ht="15.95" customHeight="1">
@@ -1551,18 +1551,18 @@
     <row r="25" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B25" s="44" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C25" s="44" t="inlineStr"/>
       <c r="D25" s="38" t="n">
-        <v>-0.006792767337715944</v>
+        <v>0.003540315591360699</v>
       </c>
       <c r="E25" s="38" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F25" s="39" t="n">
-        <v>-0.6479566188961121</v>
+        <v>0.9304802275060171</v>
       </c>
       <c r="G25" s="45" t="n"/>
     </row>
@@ -1575,13 +1575,13 @@
       </c>
       <c r="C26" s="47" t="inlineStr"/>
       <c r="D26" s="42" t="n">
-        <v>-0.004222834301844669</v>
+        <v>-0.003762527415076211</v>
       </c>
       <c r="E26" s="42" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F26" s="43" t="n">
-        <v>-0.3641047658415745</v>
+        <v>-0.3268800913895721</v>
       </c>
       <c r="G26" s="48" t="n"/>
       <c r="H26" s="49" t="n"/>
@@ -1595,13 +1595,13 @@
       </c>
       <c r="C27" s="47" t="inlineStr"/>
       <c r="D27" s="42" t="n">
-        <v>0.02029236675452073</v>
+        <v>0.01900390387702355</v>
       </c>
       <c r="E27" s="42" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F27" s="43" t="n">
-        <v>0.5750478217422147</v>
+        <v>0.5399042482493008</v>
       </c>
       <c r="G27" s="48" t="n"/>
     </row>
@@ -1614,13 +1614,13 @@
       </c>
       <c r="C28" s="47" t="inlineStr"/>
       <c r="D28" s="42" t="n">
-        <v>0.05104003630560738</v>
+        <v>0.049561787881373</v>
       </c>
       <c r="E28" s="42" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F28" s="43" t="n">
-        <v>0.7101928838069984</v>
+        <v>0.6905140317219937</v>
       </c>
       <c r="G28" s="48" t="n"/>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="C29" s="47" t="inlineStr"/>
       <c r="D29" s="42" t="n">
-        <v>0.1365371077816122</v>
+        <v>0.1324920929995024</v>
       </c>
       <c r="E29" s="42" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F29" s="43" t="n">
-        <v>0.9236905060033455</v>
+        <v>0.8951198555563813</v>
       </c>
       <c r="G29" s="48" t="n"/>
     </row>
     <row r="30" ht="15.95" customFormat="1" customHeight="1" s="35">
-      <c r="A30" s="51" t="n"/>
+      <c r="A30" s="50" t="n"/>
       <c r="B30" s="47" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C30" s="47" t="inlineStr"/>
       <c r="D30" s="42" t="n">
-        <v>0.01627712456510122</v>
+        <v>0.2316904054515956</v>
       </c>
       <c r="E30" s="42" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F30" s="43" t="n">
-        <v>0.5017760125873019</v>
+        <v>0.8336272244692556</v>
       </c>
       <c r="G30" s="48" t="n"/>
     </row>
@@ -1666,207 +1666,226 @@
       <c r="A31" s="51" t="n"/>
       <c r="B31" s="47" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C31" s="47" t="inlineStr"/>
       <c r="D31" s="42" t="n">
-        <v>0.1585779059091381</v>
+        <v>0.02014938393539012</v>
       </c>
       <c r="E31" s="42" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F31" s="43" t="n">
-        <v>1.107907901087513</v>
+        <v>0.5294752456221474</v>
       </c>
       <c r="G31" s="48" t="n"/>
     </row>
     <row r="32" ht="15.95" customFormat="1" customHeight="1" s="35">
-      <c r="A32" s="50" t="n"/>
+      <c r="A32" s="51" t="n"/>
       <c r="B32" s="47" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C32" s="47" t="inlineStr"/>
       <c r="D32" s="42" t="n">
-        <v>0.0848787242567608</v>
+        <v>0.1585779059091381</v>
       </c>
       <c r="E32" s="42" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F32" s="43" t="n">
-        <v>0.7772426302278228</v>
+        <v>1.107907901087513</v>
       </c>
       <c r="G32" s="48" t="n"/>
     </row>
     <row r="33" ht="15.95" customFormat="1" customHeight="1" s="35">
-      <c r="A33" s="51" t="n"/>
+      <c r="A33" s="50" t="n"/>
       <c r="B33" s="47" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C33" s="47" t="inlineStr"/>
       <c r="D33" s="42" t="n">
-        <v>2.47846889</v>
+        <v>0.0848787242567608</v>
       </c>
       <c r="E33" s="42" t="n">
-        <v>1.631563002366734</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F33" s="43" t="n">
-        <v>1.519076423285371</v>
+        <v>0.7772426302278228</v>
       </c>
       <c r="G33" s="48" t="n"/>
     </row>
-    <row r="34" ht="15.95" customHeight="1">
-      <c r="A34" s="13" t="n"/>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="26.1" customHeight="1">
+    <row r="34" ht="15.95" customFormat="1" customHeight="1" s="35">
+      <c r="A34" s="51" t="n"/>
+      <c r="B34" s="47" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C34" s="47" t="inlineStr"/>
+      <c r="D34" s="42" t="n">
+        <v>2.49172269</v>
+      </c>
+      <c r="E34" s="42" t="n">
+        <v>1.645878427477672</v>
+      </c>
+      <c r="F34" s="43" t="n">
+        <v>1.513916610365077</v>
+      </c>
+      <c r="G34" s="48" t="n"/>
+    </row>
+    <row r="35" ht="15.95" customHeight="1">
       <c r="A35" s="13" t="n"/>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="26.1" customHeight="1">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="34" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="34" t="n"/>
-      <c r="G35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="15.95" customHeight="1">
-      <c r="A36" s="17" t="n"/>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="52" t="n">
-        <v>132976075.57</v>
-      </c>
-      <c r="F36" s="31" t="n"/>
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n"/>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="34" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="17" t="n"/>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C37" s="16" t="n"/>
       <c r="D37" s="16" t="n"/>
       <c r="E37" s="52" t="n">
-        <v>129363890.4494841</v>
+        <v>133482746.26</v>
       </c>
       <c r="F37" s="31" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
       <c r="A38" s="17" t="n"/>
-      <c r="B38" s="19" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="52" t="n">
+        <v>129684058.2989683</v>
+      </c>
+      <c r="F38" s="31" t="n"/>
       <c r="G38" s="4" t="n"/>
     </row>
     <row r="39" ht="15.95" customHeight="1">
-      <c r="A39" s="23" t="n"/>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="A39" s="17" t="n"/>
+      <c r="B39" s="19" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="A40" s="23" t="n"/>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="21" t="inlineStr">
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="15.95" customHeight="1">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C40" s="21" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>2015-09-03</t>
         </is>
       </c>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="24" t="n"/>
-      <c r="F40" s="24" t="n"/>
-      <c r="G40" s="4" t="n"/>
-    </row>
-    <row r="41" ht="15.95" customHeight="1">
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="26" t="n"/>
       <c r="D41" s="24" t="n"/>
       <c r="E41" s="24" t="n"/>
       <c r="F41" s="24" t="n"/>
       <c r="G41" s="4" t="n"/>
     </row>
-    <row r="42" ht="51.75" customHeight="1">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="57" t="inlineStr">
+    <row r="42" ht="15.95" customHeight="1">
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="24" t="n"/>
+      <c r="E42" s="24" t="n"/>
+      <c r="F42" s="24" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="51.75" customHeight="1">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="59" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="59" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="27" t="n"/>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="27" t="n"/>
-      <c r="F44" s="27" t="n"/>
+      <c r="B44" s="57" t="n"/>
       <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
-      <c r="B45" s="28" t="n"/>
-      <c r="C45" s="29" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="12" t="n"/>
+      <c r="B45" s="27" t="n"/>
+      <c r="C45" s="27" t="n"/>
+      <c r="D45" s="27" t="n"/>
+      <c r="E45" s="27" t="n"/>
+      <c r="F45" s="27" t="n"/>
       <c r="G45" s="4" t="n"/>
     </row>
     <row r="46">
+      <c r="A46" s="4" t="n"/>
       <c r="B46" s="28" t="n"/>
       <c r="C46" s="29" t="n"/>
       <c r="D46" s="12" t="n"/>
       <c r="E46" s="12" t="n"/>
       <c r="F46" s="12" t="n"/>
+      <c r="G46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="28" t="n"/>
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="12" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B42:F42"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="84" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="82"/>
 </worksheet>
 </file>